--- a/artfynd/A 14114-2022 artfynd.xlsx
+++ b/artfynd/A 14114-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14114-2022 artfynd.xlsx
+++ b/artfynd/A 14114-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>13057895</v>
       </c>
       <c r="B2" t="n">
-        <v>42718</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>420450.8984825932</v>
+        <v>420451</v>
       </c>
       <c r="R2" t="n">
-        <v>6611712.27868887</v>
+        <v>6611712</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -762,19 +757,9 @@
           <t>2004-06-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2004-06-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -803,6 +788,238 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133779374</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57964</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102119</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Göktyta</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Jynx torquilla</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Prästbråten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>420301</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6611829</v>
+      </c>
+      <c r="S3" t="n">
+        <v>30</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Forshaga</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nedre Ullerud</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Dan Mangsbo</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Dan Mangsbo</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>13057631</v>
+      </c>
+      <c r="B4" t="n">
+        <v>43378</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>201075</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Brunfläckig pärlemorfjäril</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Boloria selene</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Deje, Mölnbacka hygge syd om Sund, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>420451</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6611712</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Forshaga</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nedre Ullerud</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2004-06-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2004-06-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Inventering Lst Värmland 2004</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14114-2022 artfynd.xlsx
+++ b/artfynd/A 14114-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13057895</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133779374</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,8 +1035,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13057631</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>